--- a/seeds/Horizonte_Conecta_Carta_Gantt.xlsx
+++ b/seeds/Horizonte_Conecta_Carta_Gantt.xlsx
@@ -9,6 +9,10 @@
     <sheet name="Asignaciones" sheetId="5" r:id="rId5"/>
     <sheet name="Criterios" sheetId="6" r:id="rId6"/>
     <sheet name="Hitos_Tareas" sheetId="7" r:id="rId7"/>
+    <sheet name="Etapas_Cambio" sheetId="8" r:id="rId8"/>
+    <sheet name="KPI_Proyecto_Hitos" sheetId="9" r:id="rId9"/>
+    <sheet name="KPI_Cambio" sheetId="10" r:id="rId10"/>
+    <sheet name="Tableros" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -72,7 +76,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jefe de Proyecto</t>
+          <t>Kevin Henríquez Rojas</t>
         </is>
       </c>
     </row>
@@ -96,7 +100,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2027-07-12</t>
+          <t>2027-08-04</t>
         </is>
       </c>
     </row>
@@ -108,7 +112,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>212809000</t>
+          <t>234109000</t>
         </is>
       </c>
     </row>
@@ -157,6 +161,722 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>2027-01-15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>codigo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>amarillo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>adicional</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Solicitudes registradas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHANGE_REQUESTS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>n°</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Total de solicitudes de cambio del proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tasa de aprobación</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHANGE_APPROVAL_RATE * 100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Aprobadas sobre decididas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tasa de rechazo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHANGE_REJECTION_RATE * 100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Rechazadas sobre decididas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tiempo medio de ciclo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CHANGE_AVG_CYCLE_HOURS / 24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>días</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Promedio de días entre registro y cierre de las solicitudes cerradas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tiempo medio de evaluación de impacto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHANGE_AVG_IMPACT_HOURS / 24</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>días</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Promedio de días entre registro y primer análisis de impacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Impacto acumulado en costo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHANGE_IMPACT_COST</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Suma del delta de costo de los cambios aprobados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Impacto acumulado en plazo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHANGE_IMPACT_DAYS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>días</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Suma del delta de plazo de los cambios aprobados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Solicitudes con evidencia completa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHANGE_EVIDENCE_COMPLETE_PCT * 100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Solicitudes con al menos una evidencia sobre el total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solicitudes fuera de SLA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CHANGE_SLA_BREACHES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>n°</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Solicitudes abiertas cuya etapa activa superó su SLA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Consumo de contingencia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHANGE_CONTINGENCY_CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Costo de cambios aprobados sobre la contingencia del proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Índice de adopción</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHANGE_ADOPTION_INDEX</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Usuarios activos sobre usuarios capacitados (variable manual).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cobertura de capacitación</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHANGE_TRAINING_COVERAGE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Usuarios capacitados sobre usuarios objetivo (variable manual).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>kpis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DB-PROYECTO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tablero del proyecto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P01,P02,P03,P04,P05,P06,P07,P08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DB-CAMBIO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tablero de gestión del cambio</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CAMBIO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C01,C02,C03,C04,C05,C06,C07,C08,C09,C10,C11,C12</t>
         </is>
       </c>
     </row>
@@ -396,7 +1116,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E-1-1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -413,7 +1133,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AC-1-1-1</t>
+          <t>AC1.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -423,12 +1143,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Actividad 1.1.1</t>
+          <t>Inicio y planificación</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>E-1-1</t>
+          <t>E1</t>
         </is>
       </c>
     </row>
@@ -450,7 +1170,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AC-1-1-1</t>
+          <t>AC1.1</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -466,7 +1186,18 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2026-10-05</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2026-10-08</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>960000</t>
         </is>
       </c>
     </row>
@@ -483,12 +1214,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hito: Kick-off realizado</t>
+          <t>Kick-off realizado</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AC-1-1-1</t>
+          <t>AC1.1</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -504,13 +1235,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A01FS</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2026-10-08</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2026-10-08</v>
       </c>
     </row>
     <row r="6">
@@ -531,7 +1268,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AC-1-1-1</t>
+          <t>AC1.1</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -547,19 +1284,30 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>H01FS</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2026-10-09</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2026-10-23</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2400000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AC-1-1-2</t>
+          <t>AC1.2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -569,12 +1317,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Actividad 1.1.2</t>
+          <t>Seguimiento y control</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>E-1-1</t>
+          <t>E1</t>
         </is>
       </c>
     </row>
@@ -596,7 +1344,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AC-1-1-2</t>
+          <t>AC1.2</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -612,19 +1360,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A02FS</t>
+          <t>A02;A40FF</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2026-10-26</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6900000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AC-1-1-3</t>
+          <t>AC1.3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -634,12 +1390,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Actividad 1.1.3</t>
+          <t>Cierre del proyecto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E-1-1</t>
+          <t>E1</t>
         </is>
       </c>
     </row>
@@ -661,7 +1417,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AC-1-1-3</t>
+          <t>AC1.3</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -677,12 +1433,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>H09FS;A42FS</t>
+          <t>H09;A42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -699,12 +1455,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hito: Cierre formal del proyecto</t>
+          <t>Cierre formal del proyecto</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AC-1-1-3</t>
+          <t>AC1.3</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -720,19 +1476,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>A04FS</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E-1-2</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -749,7 +1505,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AC-1-2-1</t>
+          <t>AC2.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -759,12 +1515,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Actividad 1.2.1</t>
+          <t>Diagnóstico de procesos actuales</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>E-1-2</t>
+          <t>E2</t>
         </is>
       </c>
     </row>
@@ -786,7 +1542,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AC-1-2-1</t>
+          <t>AC2.1</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -802,12 +1558,23 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>H01FS</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2026-10-09</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2026-10-19</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3006720</t>
         </is>
       </c>
     </row>
@@ -829,7 +1596,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AC-1-2-1</t>
+          <t>AC2.1</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -845,19 +1612,30 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>A05FS</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2026-10-20</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2026-10-23</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>704000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AC-1-2-2</t>
+          <t>AC2.2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -867,12 +1645,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Actividad 1.2.2</t>
+          <t>Requisitos, indicadores y backlog</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>E-1-2</t>
+          <t>E2</t>
         </is>
       </c>
     </row>
@@ -894,7 +1672,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AC-1-2-2</t>
+          <t>AC2.2</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -910,12 +1688,23 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A06FS</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2026-10-26</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2026-11-09</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2032800</t>
         </is>
       </c>
     </row>
@@ -937,7 +1726,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AC-1-2-2</t>
+          <t>AC2.2</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -953,12 +1742,23 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A06FS</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>2026-10-26</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2026-11-03</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1288000</t>
         </is>
       </c>
     </row>
@@ -980,7 +1780,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AC-1-2-2</t>
+          <t>AC2.2</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -996,12 +1796,23 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>A07FS;A08FS</t>
+          <t>A07;A08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2026-11-10</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2026-11-11</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>416000</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1829,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hito: Alcance aprobado</t>
+          <t>Alcance aprobado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AC-1-2-2</t>
+          <t>AC2.2</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1039,19 +1850,25 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A09FS</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2026-11-11</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2026-11-11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E-1-3</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1068,7 +1885,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AC-1-3-1</t>
+          <t>AC3.1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1078,12 +1895,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Actividad 1.3.1</t>
+          <t>Arquitectura, integraciones y datos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>E-1-3</t>
+          <t>E3</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1922,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AC-1-3-1</t>
+          <t>AC3.1</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1121,12 +1938,23 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>H01SS</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2026-10-09</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2026-10-23</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>3971000</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1976,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AC-1-3-1</t>
+          <t>AC3.1</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1164,19 +1992,30 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>A06FS;A10FS</t>
+          <t>A06;A10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2026-10-26</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2026-11-19</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5009920</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AC-1-3-2</t>
+          <t>AC3.2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1186,12 +2025,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Actividad 1.3.2</t>
+          <t>Diseño UX/UI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>E-1-3</t>
+          <t>E3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +2052,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AC-1-3-2</t>
+          <t>AC3.2</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1229,12 +2068,23 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>H02FS</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>2026-11-12</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2026-12-09</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3833760</t>
         </is>
       </c>
     </row>
@@ -1251,12 +2101,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hito: Diseño de solución aprobado</t>
+          <t>Diseño de solución aprobado</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AC-1-3-2</t>
+          <t>AC3.2</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1272,19 +2122,25 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A11FS;A12FS</t>
+          <t>A11;A12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2026-12-09</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2026-12-09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E-1-4</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1301,7 +2157,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AC-1-4-1</t>
+          <t>AC4.1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1311,12 +2167,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Actividad 1.4.1</t>
+          <t>Ambientes cloud</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>E-1-4</t>
+          <t>E4</t>
         </is>
       </c>
     </row>
@@ -1338,7 +2194,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AC-1-4-1</t>
+          <t>AC4.1</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1354,19 +2210,30 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>A11FS</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>2026-11-20</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2026-12-11</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>7080800</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AC-1-4-2</t>
+          <t>AC4.2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1376,19 +2243,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Actividad 1.4.2</t>
+          <t>Núcleo y app móvil offline</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E-1-4</t>
+          <t>E4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1398,40 +2265,51 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Desarrollar núcleo: usuarios, roles por obra, auditoría y maestros</t>
+          <t>Desarrollar la app móvil offline y probarla en terreno</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AC-1-4-2</t>
+          <t>AC4.2</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2026-12-14</v>
+        <v>2026-12-10</v>
       </c>
       <c r="F32" t="n">
-        <v>2027-01-04</v>
+        <v>2027-01-06</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>H03FS;A13FS</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>2026-12-10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2027-01-06</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>7050240</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1441,33 +2319,44 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Desarrollar la app móvil offline y probarla en terreno</t>
+          <t>Desarrollar núcleo: usuarios, roles por obra, auditoría y maestros</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AC-1-4-2</t>
+          <t>AC4.2</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2026-12-10</v>
+        <v>2026-12-14</v>
       </c>
       <c r="F33" t="n">
+        <v>2027-01-04</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>H03;A13</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>2026-12-14</v>
+      </c>
+      <c r="K33" t="n">
         <v>2027-01-06</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>H03FS</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.0</t>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>5752320</t>
         </is>
       </c>
     </row>
@@ -1484,12 +2373,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hito: Plataforma base operativa</t>
+          <t>Plataforma base operativa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AC-1-4-2</t>
+          <t>AC4.2</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1505,19 +2394,25 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>A14FS;A15FS;A16FS</t>
+          <t>A14;A15;A16</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2027-01-08</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2027-01-08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>E-1-5</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1534,7 +2429,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AC-1-5-1</t>
+          <t>AC5.1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1544,12 +2439,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Actividad 1.5.1</t>
+          <t>Identidad y repositorio Microsoft</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>E-1-5</t>
+          <t>E5</t>
         </is>
       </c>
     </row>
@@ -1571,7 +2466,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AC-1-5-1</t>
+          <t>AC5.1</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1587,19 +2482,30 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>A13FS;A10FS</t>
+          <t>A13;A10</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2026-12-14</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2027-01-08</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>3893760</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AC-1-5-2</t>
+          <t>AC5.2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1609,12 +2515,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Actividad 1.5.2</t>
+          <t>Sistema de compras y ERP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>E-1-5</t>
+          <t>E5</t>
         </is>
       </c>
     </row>
@@ -1636,7 +2542,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AC-1-5-2</t>
+          <t>AC5.2</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1652,12 +2558,20 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>A16FF</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>2027-01-11</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>373856</t>
         </is>
       </c>
     </row>
@@ -1679,7 +2593,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AC-1-5-2</t>
+          <t>AC5.2</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1695,19 +2609,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>A17SF</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>E-1-6</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1724,7 +2638,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AC-1-6-1</t>
+          <t>AC6.1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1734,12 +2648,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Actividad 1.6.1</t>
+          <t>Módulo de avance de obra</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E-1-6</t>
+          <t>E6</t>
         </is>
       </c>
     </row>
@@ -1761,7 +2675,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AC-1-6-1</t>
+          <t>AC6.1</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1777,12 +2691,20 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>H04FS</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>2027-01-11</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1036800</t>
         </is>
       </c>
     </row>
@@ -1804,7 +2726,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AC-1-6-1</t>
+          <t>AC6.1</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1820,19 +2742,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>H04FS</t>
+          <t>H04;A19SS</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>2027-01-11</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>633600</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AC-1-6-2</t>
+          <t>AC6.2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1842,12 +2772,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Actividad 1.6.2</t>
+          <t>Módulo de observaciones técnicas</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E-1-6</t>
+          <t>E6</t>
         </is>
       </c>
     </row>
@@ -1869,7 +2799,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AC-1-6-2</t>
+          <t>AC6.2</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1885,19 +2815,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>H04FS</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>2027-01-11</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1478400</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AC-1-6-3</t>
+          <t>AC6.3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1907,12 +2845,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Actividad 1.6.3</t>
+          <t>Módulo de planos vigentes</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E-1-6</t>
+          <t>E6</t>
         </is>
       </c>
     </row>
@@ -1934,7 +2872,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AC-1-6-3</t>
+          <t>AC6.3</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1950,19 +2888,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>A21FS;A16FS</t>
+          <t>A21;A16</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>E-1-7</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1979,7 +2917,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AC-1-7-1</t>
+          <t>AC7.1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1989,12 +2927,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Actividad 1.7.1</t>
+          <t>Módulo de materiales</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>E-1-7</t>
+          <t>E7</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2954,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AC-1-7-1</t>
+          <t>AC7.1</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2032,19 +2970,19 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>A29FS;A17FS</t>
+          <t>A29;A17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AC-1-7-2</t>
+          <t>AC7.2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2054,12 +2992,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Actividad 1.7.2</t>
+          <t>Módulo de subcontratos y estados de pago</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>E-1-7</t>
+          <t>E7</t>
         </is>
       </c>
     </row>
@@ -2081,7 +3019,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AC-1-7-2</t>
+          <t>AC7.2</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2097,19 +3035,19 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>A22FS</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AC-1-7-3</t>
+          <t>AC7.3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2119,12 +3057,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Actividad 1.7.3</t>
+          <t>Tablero ejecutivo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>E-1-7</t>
+          <t>E7</t>
         </is>
       </c>
     </row>
@@ -2146,7 +3084,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AC-1-7-3</t>
+          <t>AC7.3</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2162,12 +3100,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>H04FS;A08FS</t>
+          <t>H04;A08</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2027-01-11</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>388642</t>
         </is>
       </c>
     </row>
@@ -2189,7 +3135,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AC-1-7-3</t>
+          <t>AC7.3</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2205,19 +3151,19 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>A25FS;A18FS</t>
+          <t>A25;A18</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>E-1-8</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2234,7 +3180,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AC-1-8-1</t>
+          <t>AC8.1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2244,12 +3190,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Actividad 1.8.1</t>
+          <t>Plan de pruebas y calidad por sprint</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>E-1-8</t>
+          <t>E8</t>
         </is>
       </c>
     </row>
@@ -2271,7 +3217,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AC-1-8-1</t>
+          <t>AC8.1</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2287,12 +3233,23 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>H02FS</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2026-11-12</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2026-11-27</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1776000</t>
         </is>
       </c>
     </row>
@@ -2314,7 +3271,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AC-1-8-1</t>
+          <t>AC8.1</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2330,19 +3287,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>H04FS</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2027-01-11</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2497600</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AC-1-8-2</t>
+          <t>AC8.2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2352,12 +3317,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Actividad 1.8.2</t>
+          <t>Pruebas de Release 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>E-1-8</t>
+          <t>E8</t>
         </is>
       </c>
     </row>
@@ -2379,7 +3344,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AC-1-8-2</t>
+          <t>AC8.2</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2395,12 +3360,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>A19FS;A20FS;A22FS;A27FS</t>
+          <t>A19;A20;A22;A27</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2422,7 +3387,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AC-1-8-2</t>
+          <t>AC8.2</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2438,12 +3403,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>A29FS</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2460,12 +3425,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hito: Release 1 aceptada</t>
+          <t>Release 1 aceptada</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AC-1-8-2</t>
+          <t>AC8.2</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2481,19 +3446,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>A30FS</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AC-1-8-3</t>
+          <t>AC8.3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2503,12 +3468,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Actividad 1.8.3</t>
+          <t>Pruebas de Release 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>E-1-8</t>
+          <t>E8</t>
         </is>
       </c>
     </row>
@@ -2530,7 +3495,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AC-1-8-3</t>
+          <t>AC8.3</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2546,12 +3511,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>A23FS;A24FS;A26FS;H05FS</t>
+          <t>A23;A24;A26;H05</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2573,7 +3538,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AC-1-8-3</t>
+          <t>AC8.3</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2589,12 +3554,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>A31FS</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2616,7 +3581,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AC-1-8-3</t>
+          <t>AC8.3</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2632,12 +3597,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>A31FS</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2654,12 +3619,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hito: Release 2 aceptada</t>
+          <t>Release 2 aceptada</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AC-1-8-3</t>
+          <t>AC8.3</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2675,19 +3640,19 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>A33FS;A32FS</t>
+          <t>A33;A32</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>E-1-9</t>
+          <t>E9</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2704,7 +3669,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AC-1-9-1</t>
+          <t>AC9.1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2714,12 +3679,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Actividad 1.9.1</t>
+          <t>Gestión del cambio y preparación de obras</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>E-1-9</t>
+          <t>E9</t>
         </is>
       </c>
     </row>
@@ -2741,7 +3706,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AC-1-9-1</t>
+          <t>AC9.1</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2757,19 +3722,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>H04FS</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>2027-01-11</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2280000</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AC-1-9-2</t>
+          <t>AC9.2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2779,12 +3752,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Actividad 1.9.2</t>
+          <t>Puesta en marcha de Release 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>E-1-9</t>
+          <t>E9</t>
         </is>
       </c>
     </row>
@@ -2806,7 +3779,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AC-1-9-2</t>
+          <t>AC9.2</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2822,12 +3795,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>A29FS;A34FS</t>
+          <t>A29;A34</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2849,7 +3822,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AC-1-9-2</t>
+          <t>AC9.2</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2865,12 +3838,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>H05FS;A35FS</t>
+          <t>H05;A35</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2887,12 +3860,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hito: Release 1 en operación en las 3 obras</t>
+          <t>Release 1 en operación en las 3 obras</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AC-1-9-2</t>
+          <t>AC9.2</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2908,12 +3881,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>A36FS</t>
+          <t>A36</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3908,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AC-1-9-2</t>
+          <t>AC9.2</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2951,19 +3924,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>H06FS</t>
+          <t>H06;A31SF</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AC-1-9-3</t>
+          <t>AC9.3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2973,12 +3946,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Actividad 1.9.3</t>
+          <t>Puesta en marcha de Release 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>E-1-9</t>
+          <t>E9</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3973,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AC-1-9-3</t>
+          <t>AC9.3</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -3016,12 +3989,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>A31FS</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3043,7 +4016,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AC-1-9-3</t>
+          <t>AC9.3</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -3059,12 +4032,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>H07FS;A38FS</t>
+          <t>H07;A38</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3081,12 +4054,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hito: Release 2 en operación en las 3 obras</t>
+          <t>Release 2 en operación en las 3 obras</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AC-1-9-3</t>
+          <t>AC9.3</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -3102,12 +4075,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>A39FS</t>
+          <t>A39</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3129,7 +4102,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AC-1-9-3</t>
+          <t>AC9.3</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -3145,19 +4118,19 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>H08FS</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AC-1-9-4</t>
+          <t>AC9.4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3167,12 +4140,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Actividad 1.9.4</t>
+          <t>Evaluación del piloto</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>E-1-9</t>
+          <t>E9</t>
         </is>
       </c>
     </row>
@@ -3194,7 +4167,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AC-1-9-4</t>
+          <t>AC9.4</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3210,12 +4183,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>A40FS</t>
+          <t>A40</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3232,12 +4205,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hito: Evaluación del piloto aprobada</t>
+          <t>Evaluación del piloto aprobada</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AC-1-9-4</t>
+          <t>AC9.4</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -3253,19 +4226,19 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>A41FS</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>E-1-10</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3282,7 +4255,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AC-1-10-1</t>
+          <t>AC10.1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3292,12 +4265,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Actividad 1.10.1</t>
+          <t>Documentación y traspaso a TI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>E-1-10</t>
+          <t>E10</t>
         </is>
       </c>
     </row>
@@ -3319,7 +4292,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AC-1-10-1</t>
+          <t>AC10.1</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3335,12 +4308,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>H08FS</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3391,12 +4364,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Analista Funcional / de Negocio 1</t>
+          <t>Jefe de Proyecto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3406,12 +4379,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Analista Funcional / de Negocio</t>
+          <t>Jefe de Proyecto</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3428,12 +4401,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analista QA 1</t>
+          <t>Analista Funcional / de Negocio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3443,12 +4416,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Analista QA</t>
+          <t>Analista Funcional / de Negocio</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3465,12 +4438,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>AR1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analista QA 2</t>
+          <t>Arquitecto de Solución</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3480,12 +4453,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Analista QA</t>
+          <t>Arquitecto de Solución</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3502,12 +4475,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>UX1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analista QA 3</t>
+          <t>Diseñador UX/UI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3517,12 +4490,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Analista QA</t>
+          <t>Diseñador UX/UI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3539,12 +4512,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analista QA 4</t>
+          <t>Desarrollador Backend 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3554,12 +4527,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Analista QA</t>
+          <t>Desarrollador Backend</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3576,12 +4549,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>BE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analista de Datos / BI 1</t>
+          <t>Desarrollador Backend 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3591,7 +4564,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Analista de Datos / BI</t>
+          <t>Desarrollador Backend</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3613,12 +4586,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>FE1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arquitecto de Solución 1</t>
+          <t>Desarrollador Frontend/Móvil 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3628,12 +4601,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arquitecto de Solución</t>
+          <t>Desarrollador Frontend/Móvil</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3650,12 +4623,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>FE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Desarrollador Backend 1</t>
+          <t>Desarrollador Frontend/Móvil 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3665,7 +4638,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Desarrollador Backend</t>
+          <t>Desarrollador Frontend/Móvil</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3687,12 +4660,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R009</t>
+          <t>IN1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Desarrollador Backend 2</t>
+          <t>Desarrollador de Integraciones</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3702,12 +4675,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Desarrollador Backend</t>
+          <t>Desarrollador de Integraciones</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3724,12 +4697,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>BI1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Desarrollador Frontend/Móvil 1</t>
+          <t>Analista de Datos / BI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3739,12 +4712,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Desarrollador Frontend/Móvil</t>
+          <t>Analista de Datos / BI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3761,12 +4734,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R011</t>
+          <t>QA1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Desarrollador Frontend/Móvil 2</t>
+          <t>Analista QA 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3776,12 +4749,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Desarrollador Frontend/Móvil</t>
+          <t>Analista QA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3798,12 +4771,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>QA2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Desarrollador de Integraciones 1</t>
+          <t>Analista QA 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3813,12 +4786,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Desarrollador de Integraciones</t>
+          <t>Analista QA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3835,12 +4808,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diseñador UX/UI 1</t>
+          <t>Ingeniero DevOps / Cloud</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3850,12 +4823,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Diseñador UX/UI</t>
+          <t>Ingeniero DevOps / Cloud</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3872,12 +4845,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>GC1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Especialista Gestión del Cambio y Capacitación 1</t>
+          <t>Especialista Gestión del Cambio y Capacitación</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3892,7 +4865,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3909,170 +4882,288 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>NL-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ingeniero DevOps / Cloud 1</t>
+          <t>Infraestructura cloud (dev, QA y producción)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HUMANO</t>
+          <t>INFRAESTRUCTURA_LICENCIA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ingeniero DevOps / Cloud</t>
+          <t>Infraestructura y licencias</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>850000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>hora</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>mes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>NL-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jefe de Proyecto 1</t>
+          <t>Licencias de herramientas del proyecto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HUMANO</t>
+          <t>INFRAESTRUCTURA_LICENCIA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jefe de Proyecto</t>
+          <t>Infraestructura y licencias</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>hora</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>usuario-mes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RE-EQ-001</t>
+          <t>NL-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tablet de obra</t>
+          <t>Licencias de tablero BI (piloto)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EQUIPAMIENTO</t>
+          <t>INFRAESTRUCTURA_LICENCIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Dispositivo</t>
+          <t>Infraestructura y licencias</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>unidad</t>
+          <t>usuario-mes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RE-INF-001</t>
+          <t>NL-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infraestructura cloud</t>
+          <t>Tablets rugerizadas para obra</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRAESTRUCTURA_LICENCIA</t>
+          <t>EQUIPAMIENTO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Equipamiento</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1200000</t>
+          <t>480000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>unidad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RE-SVC-001</t>
+          <t>NL-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Servicio externo API compras</t>
+          <t>Kits de conectividad para obras</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>EQUIPAMIENTO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Equipamiento</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>950000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NL-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Soporte del proveedor del sistema de compras</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>SERVICIO_EXTERNO</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Servicio externo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>35000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NL-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Soporte del proveedor del ERP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SERVICIO_EXTERNO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Servicio externo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>38000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NL-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Prueba de seguridad externa (ethical hacking)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SERVICIO_EXTERNO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Servicio externo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4800000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NL-09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Traslados y viáticos a obras piloto</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SERVICIO_EXTERNO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Servicio externo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3600000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>global</t>
         </is>
       </c>
     </row>
@@ -4123,7 +5214,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4145,7 +5236,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4167,7 +5258,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4189,7 +5280,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4211,7 +5302,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4233,7 +5324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>UX1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4255,7 +5346,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4277,7 +5368,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4299,7 +5390,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>BI1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4321,7 +5412,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4343,7 +5434,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4365,7 +5456,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>IN1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4387,7 +5478,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>AR1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4409,7 +5500,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>UX1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4431,7 +5522,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4453,12 +5544,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4470,17 +5561,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>BE2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>288.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4492,12 +5583,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>FE1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4514,17 +5605,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>FE2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4536,17 +5627,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>IN1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4558,17 +5649,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>IN1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4580,17 +5671,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>IN1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4602,17 +5693,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4624,17 +5715,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>FE1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4646,17 +5737,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>BE2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4668,17 +5759,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>FE2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4690,17 +5781,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>BE2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4712,17 +5803,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>FE2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4734,17 +5825,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>BE2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4756,17 +5847,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>FE1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4778,17 +5869,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4800,17 +5891,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>FE2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4822,17 +5913,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>BI1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4844,44 +5935,44 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>BI1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>QA1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
@@ -4893,7 +5984,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4915,7 +6006,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>UX1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4937,7 +6028,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>QA2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4954,44 +6045,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>AR1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -5003,7 +6094,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>QA1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5020,88 +6111,88 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>BE2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>FE1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>QA2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
@@ -5113,7 +6204,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>QA1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5135,7 +6226,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>QA2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5157,7 +6248,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5179,7 +6270,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>BE2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5196,83 +6287,83 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>FE2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>FE1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>QA1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5284,17 +6375,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5306,176 +6397,176 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>GC1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A36</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A35</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>GC1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>A37</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>GC1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A37</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A40</t>
+          <t>A38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>GC1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A40</t>
+          <t>A39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
@@ -5487,7 +6578,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>GC1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5509,7 +6600,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5526,17 +6617,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A40</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5548,17 +6639,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A40</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>FE2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5575,7 +6666,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5592,17 +6683,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>AF1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5614,17 +6705,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>BI1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5641,7 +6732,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>AR1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5652,6 +6743,339 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A42</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A42</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GC1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NL-01</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NL-01</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NL-02</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NL-03</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>58.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NL-03</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>58.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A40</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NL-03</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>58.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A34</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NL-04</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>A34</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NL-05</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NL-06</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NL-06</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NL-07</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>A32</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NL-08</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NL-09</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NL-09</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>A35</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NL-09</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>A37</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NL-09</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>A40</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NL-09</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5707,39 +7131,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Revisión del acta firmada en comité</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hito (responsable: Jefe de Proyecto)</t>
+          <t>Jefe de Proyecto</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CR-H10-01</t>
+          <t>CR-H01-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Acta de cierre firmada</t>
+          <t>A01: El patrocinador firma el acta de kick-off</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Inspección del resultado verificable: Acta de kick-off y matriz RACI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hito (responsable: Jefe de Proyecto)</t>
+          <t>Jefe de Proyecto</t>
         </is>
       </c>
     </row>
@@ -5761,201 +7185,579 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Revisión del acta firmada en comité</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hito (responsable: Analista Funcional / de Negocio)</t>
+          <t>Analista Funcional / de Negocio</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CR-H03-01</t>
+          <t>CR-H02-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arquitectura y prototipo aprobados</t>
+          <t>A09: El comité aprueba el alcance y decide sobre Prevención de Riesgos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Inspección del resultado verificable: Backlog priorizado y acta de alcance</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hito (responsable: Diseñador UX/UI)</t>
+          <t>Analista Funcional / de Negocio + Jefe de Proyecto</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CR-H04-01</t>
+          <t>CR-H03-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Núcleo, app offline y SSO funcionando en QA</t>
+          <t>Arquitectura y prototipo aprobados</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Revisión del acta firmada en comité</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hito (responsable: Desarrollador Backend)</t>
+          <t>Diseñador UX/UI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CR-H05-01</t>
+          <t>CR-H03-02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Acta UAT R1 firmada</t>
+          <t>A11: TI corporativa aprueba la arquitectura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Inspección del resultado verificable: Documento de arquitectura y modelo de datos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hito (responsable: Analista QA)</t>
+          <t>Arquitecto de Solución</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CR-H07-01</t>
+          <t>CR-H03-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Acta UAT R2 e informe de seguridad aprobados</t>
+          <t>A12: ≥ 80 % de tareas completadas sin ayuda en la prueba</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Inspección del resultado verificable: Prototipo validado</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hito (responsable: Analista QA)</t>
+          <t>Diseñador UX/UI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CR-H06-01</t>
+          <t>CR-H04-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Usuarios registran datos reales</t>
+          <t>Núcleo, app offline y SSO funcionando en QA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Revisión del acta firmada en comité</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hito (responsable: Especialista Gestión del Cambio y Capacitación)</t>
+          <t>Desarrollador Backend</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CR-H08-01</t>
+          <t>CR-H04-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Primer EP y primera recepción en producción</t>
+          <t>A14: Usuario sin permiso es rechazado; maestros cargados</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Revisión del acta y evidencia del entregable</t>
+          <t>Inspección del resultado verificable: Núcleo desplegado en QA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hito (responsable: Especialista Gestión del Cambio y Capacitación)</t>
+          <t>Desarrollador Backend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>H04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CR-H04-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A15: 0 registros perdidos en 50 operaciones sin señal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: App base con sincronización</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Desarrollador Frontend/Móvil</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CR-H04-04</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A16: Login corporativo funciona y se lee la versión vigente de un plano</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: SSO y conector documental en QA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Desarrollador de Integraciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CR-H05-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Acta UAT R1 firmada</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Revisión del acta firmada en comité</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Analista QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CR-H05-02</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A30: Usuarios clave firman el acta</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: Acta UAT R1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Analista QA + Analista Funcional / de Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CR-H06-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Usuarios registran datos reales</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Revisión del acta firmada en comité</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Especialista Gestión del Cambio y Capacitación</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CR-H06-02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A36: Smoke test aprobado</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: R1 en producción</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ingeniero DevOps / Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CR-H07-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Acta UAT R2 e informe de seguridad aprobados</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Revisión del acta firmada en comité</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Analista QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CR-H07-02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A33: Usuarios, Finanzas y Gerencia firman el acta</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: Acta UAT R2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Analista QA + Analista Funcional / de Negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CR-H07-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A32: Sin hallazgos críticos ni altos abiertos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: Informe de seguridad</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ingeniero DevOps / Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CR-H08-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Primer EP y primera recepción en producción</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Revisión del acta firmada en comité</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Especialista Gestión del Cambio y Capacitación</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CR-H08-02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A39: Smoke test aprobado</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: R2 en producción</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ingeniero DevOps / Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>H09</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>CR-H09-01</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Acta de comité con decisión de escalamiento</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Revisión del acta y evidencia del entregable</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hito (responsable: Jefe de Proyecto)</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Revisión del acta firmada en comité</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Jefe de Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CR-H09-02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A41: El comité decide el escalamiento</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: Informe de evaluación y plan de escalamiento</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Jefe de Proyecto + Analista Funcional / de Negocio + Analista de Datos / BI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CR-H10-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Acta de cierre firmada</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Revisión del acta firmada en comité</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Jefe de Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CR-H10-02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A04: El patrocinador firma el acta de cierre</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Inspección del resultado verificable: Acta de cierre firmada</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Jefe de Proyecto</t>
         </is>
       </c>
     </row>
@@ -5993,24 +7795,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A11</t>
         </is>
       </c>
     </row>
@@ -6022,19 +7824,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A14</t>
         </is>
       </c>
     </row>
@@ -6046,7 +7848,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A15</t>
         </is>
       </c>
     </row>
@@ -6058,31 +7860,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A36</t>
         </is>
       </c>
     </row>
@@ -6113,36 +7915,765 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A36</t>
+          <t>A39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>secuencia</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sla_horas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CS01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Registro</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CS02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Revisión inicial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CS03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Clasificación y prioridad</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CS04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Análisis de impacto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CS05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Revisión del comité</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CS06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CS07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Planificación del cambio</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CS08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CS09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CS10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cierre y línea base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>codigo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>amarillo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>adicional</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Índice de desempeño del cronograma (SPI)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EV / PV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>índice</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valor ganado sobre valor planificado a la fecha de corte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Índice de desempeño de costo (CPI)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EV / AC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>índice</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Valor ganado sobre costo real a la fecha de corte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Variación del cronograma (SV)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EV - PV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2000000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Diferencia entre valor ganado y valor planificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Variación de costo (CV)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EV - AC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-2000000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Diferencia entre valor ganado y costo real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Desviación de avance físico</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AVANCE_REAL - AVANCE_PLAN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pp</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Avance real menos avance planificado, en puntos porcentuales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Actividades atrasadas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>count(ACTIVIDADES_ATRASADAS) / count(ACTIVIDADES) * 100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Subactividades iniciadas o vencidas con avance bajo lo planificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hitos cumplidos a tiempo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MILESTONES_ON_TIME_PCT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HITO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Hitos cumplidos en o antes de su fecha base, sobre hitos cumplidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Desviación del hito de cierre</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLOSING_MILESTONE_DEVIATION</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HITO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>días</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Días hábiles entre la fecha proyectada y la fecha base del cierre.</t>
         </is>
       </c>
     </row>
